--- a/data/catalogue/task2-sources.xlsx
+++ b/data/catalogue/task2-sources.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Visa, IHS, London living, flights until Ambrosh / a sourced fare</t>
+          <t>Flights still PLACEHOLDER. Visa, IHS and London living sourced 2026-10-30.</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -737,7 +737,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells on the GOV.UK tab are for Ambrosh: visa fee, IHS, and London living / maintenance, each with URL and date. Do not type invented numbers into the catalogue.</t>
+          <t>GOV.UK visa (£558), IHS (£776/year student) and London living (£13,761 visa financial requirement) were sourced 2026-10-30. Flights stay PLACEHOLDER. Yellow cells mean still missing. Do not invent a fare.</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -788,7 +788,7 @@
           <t>1. robots.txt — course/scholarship/India paths allowed; no login.
 2. Scrapy polite crawl (3s delay, 1 concurrent) into data/raw.
 3. Live check of UEL facts against the page (browser sample: Business Management BSc, Computer Science BSc, International Business Management MSc, scholarships, India).
-4. GOV.UK visa / IHS / living — Ambrosh.
+4. GOV.UK visa £558 / IHS £776 / London living £13,761 — sourced 2026-10-30.
 5. RBI INR/GBP reference from rbi.org.in, 1.00pm 28 Oct 2026, 126.4657 (FBIL).</t>
         </is>
       </c>
@@ -2118,13 +2118,11 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh GOV.UK</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>13761</v>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
@@ -2133,12 +2131,12 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Spot-check London living / maintenance.</t>
+          <t>Visa financial requirement £1,529 × 9 months. Not a personal spend forecast; not extra rent on halls.</t>
         </is>
       </c>
     </row>
@@ -2150,13 +2148,11 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh GOV.UK</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>558</v>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
@@ -2165,12 +2161,12 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Spot-check student visa fee.</t>
+          <t>Student visa from outside the UK.</t>
         </is>
       </c>
     </row>
@@ -2182,27 +2178,25 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh GOV.UK</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>776</v>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/healthcare-immigration-application</t>
+          <t>https://www.gov.uk/healthcare-immigration-application/how-much-pay</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Spot-check Immigration Health Surcharge.</t>
+          <t>Student IHS rate per year. Year-one stack uses one year.</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5560,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -5576,7 +5570,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -5586,7 +5580,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Awaiting Ambrosh GOV.UK spot-check.</t>
+          <t>GOV.UK London financial requirement £1,529/month × 9 months. Visa maintenance figure, not a personal spend forecast. Do not add typical UEL room on top of this as a second rent.</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5592,7 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>558</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -5608,7 +5602,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -5618,7 +5612,7 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Awaiting Ambrosh GOV.UK spot-check.</t>
+          <t>Student visa from outside the UK.</t>
         </is>
       </c>
     </row>
@@ -5630,17 +5624,17 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>776</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/healthcare-immigration-application</t>
+          <t>https://www.gov.uk/healthcare-immigration-application/how-much-pay</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -5650,7 +5644,7 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>Awaiting Ambrosh GOV.UK spot-check.</t>
+          <t>Student IHS rate per year. A longer visa costs more; year-one stack uses one year.</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5795,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5834,69 +5828,75 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Student visa fee</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
+          <t>Student visa fee (from outside the UK)</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>558</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>https://www.gov.uk/student-visa</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh</t>
+          <t>govuk-spot-check</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Immigration Health Surcharge</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/healthcare-immigration-application</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr"/>
+          <t>Immigration Health Surcharge (student rate, one year)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>776</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/healthcare-immigration-application/how-much-pay</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh</t>
+          <t>govuk-spot-check</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>London living / maintenance</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
+          <t>London living / maintenance (visa financial requirement, 9 months)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>13761</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>https://www.gov.uk/student-visa/money</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Ambrosh</t>
+          <t>govuk-spot-check</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Paste the figure, the page URL, and the date you checked. Build will copy them into costs.json and sources.csv.</t>
+          <t>Living is the GOV.UK visa financial requirement, not a personal spend forecast. Do not add UEL halls on top of it as a second rent. Flights stay PLACEHOLDER.</t>
         </is>
       </c>
       <c r="B6" s="9" t="n"/>
